--- a/data/trans_orig/P26-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P26-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182449</t>
+          <t>181704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233714</t>
+          <t>231763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340328</t>
+          <t>340955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404366</t>
+          <t>404296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>539692</t>
+          <t>538590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>618072</t>
+          <t>618722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>699351</t>
+          <t>701302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>750616</t>
+          <t>751361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>729598</t>
+          <t>729668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>793636</t>
+          <t>793009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1448957</t>
+          <t>1448307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1527337</t>
+          <t>1528439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>495354</t>
+          <t>495342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>575660</t>
+          <t>574113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>610960</t>
+          <t>607479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>690372</t>
+          <t>685625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1125008</t>
+          <t>1131579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1240125</t>
+          <t>1238091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1026942</t>
+          <t>1028489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1107248</t>
+          <t>1107260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>827709</t>
+          <t>832456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>907121</t>
+          <t>910602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1880558</t>
+          <t>1882592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1995675</t>
+          <t>1989104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113326</t>
+          <t>113857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>153427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109107</t>
+          <t>108526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146844</t>
+          <t>146219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232522</t>
+          <t>235315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287535</t>
+          <t>293663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359894</t>
+          <t>362772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>402873</t>
+          <t>402342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293497</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331234</t>
+          <t>331815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669005</t>
+          <t>662877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>724018</t>
+          <t>721225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>819766</t>
+          <t>824973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>919521</t>
+          <t>926295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1092109</t>
+          <t>1093745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1200621</t>
+          <t>1202815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1943595</t>
+          <t>1943490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2094258</t>
+          <t>2096193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2132345</t>
+          <t>2125571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2232100</t>
+          <t>2226893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1891766</t>
+          <t>1889572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2000278</t>
+          <t>1998642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4049995</t>
+          <t>4048060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4200658</t>
+          <t>4200763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215317</t>
+          <t>218026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272093</t>
+          <t>271218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385878</t>
+          <t>390060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>457103</t>
+          <t>454523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615979</t>
+          <t>616624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>703952</t>
+          <t>704497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654263</t>
+          <t>655138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>711039</t>
+          <t>708330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>763875</t>
+          <t>766455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>835100</t>
+          <t>830918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1443382</t>
+          <t>1442837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1531355</t>
+          <t>1530710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>660171</t>
+          <t>658286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>743567</t>
+          <t>747103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>717906</t>
+          <t>715940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>798965</t>
+          <t>797238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1402481</t>
+          <t>1398218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1520213</t>
+          <t>1525386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1153189</t>
+          <t>1149653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1236585</t>
+          <t>1238470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>906400</t>
+          <t>908127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>987459</t>
+          <t>989425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2081908</t>
+          <t>2076735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2199640</t>
+          <t>2203903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112875</t>
+          <t>113649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154922</t>
+          <t>155993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104640</t>
+          <t>106905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145599</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230407</t>
+          <t>232179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289621</t>
+          <t>290567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295446</t>
+          <t>294375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337493</t>
+          <t>336719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286771</t>
+          <t>286197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327730</t>
+          <t>325465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593117</t>
+          <t>592171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652331</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1026583</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1134798</t>
+          <t>1134847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1242782</t>
+          <t>1243290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1363079</t>
+          <t>1361347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2306889</t>
+          <t>2296987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2469336</t>
+          <t>2459305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2138682</t>
+          <t>2138633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2246897</t>
+          <t>2250890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1995634</t>
+          <t>1997366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2115931</t>
+          <t>2115423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4162858</t>
+          <t>4172889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4325305</t>
+          <t>4335207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130115</t>
+          <t>130415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174534</t>
+          <t>173515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163642</t>
+          <t>160353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211362</t>
+          <t>210868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302093</t>
+          <t>304141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365128</t>
+          <t>371382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503297</t>
+          <t>504316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547716</t>
+          <t>547416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667146</t>
+          <t>667640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>714866</t>
+          <t>718155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1191211</t>
+          <t>1184957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1254246</t>
+          <t>1252198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503376</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>582215</t>
+          <t>584063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>536777</t>
+          <t>534892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>618934</t>
+          <t>616659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1062722</t>
+          <t>1055130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1180415</t>
+          <t>1176130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1382569</t>
+          <t>1380721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1461408</t>
+          <t>1461526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1268726</t>
+          <t>1271001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1350883</t>
+          <t>1352768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2672029</t>
+          <t>2676314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2789722</t>
+          <t>2797314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80667</t>
+          <t>81106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121180</t>
+          <t>117640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>96212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133059</t>
+          <t>134484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186283</t>
+          <t>185805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241839</t>
+          <t>240486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>370414</t>
+          <t>373954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410927</t>
+          <t>410488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373095</t>
+          <t>371670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>411026</t>
+          <t>409942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>755909</t>
+          <t>757262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811465</t>
+          <t>811943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>743215</t>
+          <t>741354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>840011</t>
+          <t>843002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>825569</t>
+          <t>827116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>926473</t>
+          <t>929912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1598283</t>
+          <t>1596195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1739216</t>
+          <t>1745470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2294198</t>
+          <t>2291207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2390994</t>
+          <t>2392855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2345849</t>
+          <t>2342410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2446753</t>
+          <t>2445206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4667315</t>
+          <t>4661061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4808248</t>
+          <t>4810336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37385</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>58306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84269</t>
+          <t>84387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>102956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141199</t>
+          <t>140257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371059</t>
+          <t>370627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>398152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533757</t>
+          <t>533639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559495</t>
+          <t>559720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>913155</t>
+          <t>914097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>951046</t>
+          <t>951398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>241583</t>
+          <t>242450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>925979</t>
+          <t>1002452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>212686</t>
+          <t>205970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>343826</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>525911</t>
+          <t>535083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1448283</t>
+          <t>1456875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1194298</t>
+          <t>1117825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1878694</t>
+          <t>1877827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1773356</t>
+          <t>1771372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1904496</t>
+          <t>1911212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2789176</t>
+          <t>2780584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3711548</t>
+          <t>3702376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47051</t>
+          <t>47593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83537</t>
+          <t>84385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55987</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>87296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112321</t>
+          <t>110960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162033</t>
+          <t>159831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523065</t>
+          <t>522217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>559551</t>
+          <t>559009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537101</t>
+          <t>535772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>567081</t>
+          <t>567077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067637</t>
+          <t>1069839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1117349</t>
+          <t>1118710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>354371</t>
+          <t>357400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1227196</t>
+          <t>1189959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350612</t>
+          <t>342393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>486463</t>
+          <t>478885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>780402</t>
+          <t>776863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1775609</t>
+          <t>1703656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1936012</t>
+          <t>1973249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2808837</t>
+          <t>2805808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2871812</t>
+          <t>2879390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3007663</t>
+          <t>3015882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4745873</t>
+          <t>4817826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5741080</t>
+          <t>5744619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P26-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P26-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181704</t>
+          <t>180658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231763</t>
+          <t>232029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340955</t>
+          <t>343205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404296</t>
+          <t>403119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538590</t>
+          <t>539914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>618722</t>
+          <t>618921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701302</t>
+          <t>701036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>751361</t>
+          <t>752407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>729668</t>
+          <t>730845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>793009</t>
+          <t>790759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1448307</t>
+          <t>1448108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1528439</t>
+          <t>1527115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>495342</t>
+          <t>496519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>574113</t>
+          <t>576650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607479</t>
+          <t>612672</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>685625</t>
+          <t>689046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1131579</t>
+          <t>1130939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1238091</t>
+          <t>1239193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1028489</t>
+          <t>1025952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1107260</t>
+          <t>1106083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>832456</t>
+          <t>829035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910602</t>
+          <t>905409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1882592</t>
+          <t>1881490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1989104</t>
+          <t>1989744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113857</t>
+          <t>113364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153427</t>
+          <t>153983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108526</t>
+          <t>107228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146219</t>
+          <t>147732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235315</t>
+          <t>233487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293663</t>
+          <t>290253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362772</t>
+          <t>362216</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>402342</t>
+          <t>402835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294122</t>
+          <t>292609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331815</t>
+          <t>333113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662877</t>
+          <t>666287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>721225</t>
+          <t>723053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>824973</t>
+          <t>818869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>926295</t>
+          <t>923660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1093745</t>
+          <t>1097897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1202815</t>
+          <t>1201372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1943490</t>
+          <t>1949927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2096193</t>
+          <t>2091256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2125571</t>
+          <t>2128206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2226893</t>
+          <t>2232997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1889572</t>
+          <t>1891015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1998642</t>
+          <t>1994490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4048060</t>
+          <t>4052997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4200763</t>
+          <t>4194326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218026</t>
+          <t>214264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271218</t>
+          <t>270357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>390060</t>
+          <t>384994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>454523</t>
+          <t>454144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616624</t>
+          <t>619482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>704497</t>
+          <t>709789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655138</t>
+          <t>655999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708330</t>
+          <t>712092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>766455</t>
+          <t>766834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>830918</t>
+          <t>835984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1442837</t>
+          <t>1437545</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1530710</t>
+          <t>1527852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>658286</t>
+          <t>661129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>747103</t>
+          <t>745327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>715940</t>
+          <t>715510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>797238</t>
+          <t>799383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1398218</t>
+          <t>1395414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1525386</t>
+          <t>1516359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1149653</t>
+          <t>1151429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1238470</t>
+          <t>1235627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908127</t>
+          <t>905982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>989425</t>
+          <t>989855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076735</t>
+          <t>2085762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2203903</t>
+          <t>2206707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>114178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155993</t>
+          <t>154991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106905</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>147839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232179</t>
+          <t>228009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290567</t>
+          <t>286127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294375</t>
+          <t>295377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336719</t>
+          <t>336190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286197</t>
+          <t>284531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325465</t>
+          <t>325639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592171</t>
+          <t>596611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>650559</t>
+          <t>654729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1022590</t>
+          <t>1017679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1134847</t>
+          <t>1129215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1243290</t>
+          <t>1239886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1361347</t>
+          <t>1361468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2296987</t>
+          <t>2304699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2459305</t>
+          <t>2466671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2138633</t>
+          <t>2144265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2250890</t>
+          <t>2255801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1997366</t>
+          <t>1997245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2115423</t>
+          <t>2118827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4172889</t>
+          <t>4165523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4335207</t>
+          <t>4327495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130415</t>
+          <t>129918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173515</t>
+          <t>173397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160353</t>
+          <t>161921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210868</t>
+          <t>214293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304141</t>
+          <t>304879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371382</t>
+          <t>371275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>504316</t>
+          <t>504434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547416</t>
+          <t>547913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667640</t>
+          <t>664215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>718155</t>
+          <t>716587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184957</t>
+          <t>1185064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1252198</t>
+          <t>1251460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503258</t>
+          <t>505551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>584063</t>
+          <t>582587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>534892</t>
+          <t>538442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>616659</t>
+          <t>622844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1055130</t>
+          <t>1060568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1176130</t>
+          <t>1174599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1380721</t>
+          <t>1382197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1461526</t>
+          <t>1459233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1271001</t>
+          <t>1264816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1352768</t>
+          <t>1349218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2676314</t>
+          <t>2677845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2797314</t>
+          <t>2791876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81106</t>
+          <t>81651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117640</t>
+          <t>122209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96212</t>
+          <t>93646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>133684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185805</t>
+          <t>187673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240486</t>
+          <t>241339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>373954</t>
+          <t>369385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410488</t>
+          <t>409943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>371670</t>
+          <t>372470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409942</t>
+          <t>412508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>757262</t>
+          <t>756409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811943</t>
+          <t>810075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>741354</t>
+          <t>744787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>843002</t>
+          <t>844381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>827116</t>
+          <t>825799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>929912</t>
+          <t>925322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1596195</t>
+          <t>1597379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1745470</t>
+          <t>1736393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2291207</t>
+          <t>2289828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2392855</t>
+          <t>2389422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2342410</t>
+          <t>2347000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2445206</t>
+          <t>2446523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4661061</t>
+          <t>4670138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4810336</t>
+          <t>4809152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50993</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>45416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69797</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>61839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84387</t>
+          <t>88597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>120790</t>
+          <t>132313</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102956</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140257</t>
+          <t>153230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>385335</t>
+          <t>429110</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370627</t>
+          <t>411965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398152</t>
+          <t>441756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>548229</t>
+          <t>601942</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533639</t>
+          <t>587596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559720</t>
+          <t>614354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>933564</t>
+          <t>1031053</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>914097</t>
+          <t>1010136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>951398</t>
+          <t>1049454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>436328</t>
+          <t>487172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>436328</t>
+          <t>487172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>436328</t>
+          <t>487172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>618026</t>
+          <t>676193</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>618026</t>
+          <t>676193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>618026</t>
+          <t>676193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1054354</t>
+          <t>1163366</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1054354</t>
+          <t>1163366</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1054354</t>
+          <t>1163366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>470434</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242450</t>
+          <t>205161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1002452</t>
+          <t>279261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>292136</t>
+          <t>315514</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205970</t>
+          <t>286687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>349368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>762570</t>
+          <t>555786</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>535083</t>
+          <t>507959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1456875</t>
+          <t>604809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1649843</t>
+          <t>1798818</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1117825</t>
+          <t>1759829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1877827</t>
+          <t>1833929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1825046</t>
+          <t>1718805</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1771372</t>
+          <t>1684951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1911212</t>
+          <t>1747632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3474889</t>
+          <t>3517623</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2780584</t>
+          <t>3468600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3702376</t>
+          <t>3565450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2120277</t>
+          <t>2039090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2120277</t>
+          <t>2039090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2120277</t>
+          <t>2039090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2117182</t>
+          <t>2034319</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2117182</t>
+          <t>2034319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2117182</t>
+          <t>2034319</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4237459</t>
+          <t>4073409</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4237459</t>
+          <t>4073409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4237459</t>
+          <t>4073409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64256</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>88821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>76425</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87296</t>
+          <t>93385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>134493</t>
+          <t>143891</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110960</t>
+          <t>121079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159831</t>
+          <t>169168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>542346</t>
+          <t>595658</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522217</t>
+          <t>574303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>559009</t>
+          <t>612623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>552831</t>
+          <t>617426</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535772</t>
+          <t>600466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>567077</t>
+          <t>631239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1095177</t>
+          <t>1213083</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1069839</t>
+          <t>1187806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1118710</t>
+          <t>1235895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>606602</t>
+          <t>663124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>606602</t>
+          <t>663124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>606602</t>
+          <t>663124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>623068</t>
+          <t>693851</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>623068</t>
+          <t>693851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>623068</t>
+          <t>693851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1229670</t>
+          <t>1356974</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1229670</t>
+          <t>1356974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1229670</t>
+          <t>1356974</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>585683</t>
+          <t>365800</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>357400</t>
+          <t>322749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1189959</t>
+          <t>408078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>432170</t>
+          <t>466190</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>430079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>478885</t>
+          <t>505565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1017853</t>
+          <t>831991</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>776863</t>
+          <t>775882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1703656</t>
+          <t>886308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2577525</t>
+          <t>2823586</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1973249</t>
+          <t>2781308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2805808</t>
+          <t>2866637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2926105</t>
+          <t>2938173</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2879390</t>
+          <t>2898798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3015882</t>
+          <t>2974284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5503629</t>
+          <t>5761758</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4817826</t>
+          <t>5707441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5744619</t>
+          <t>5817867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3163208</t>
+          <t>3189386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3163208</t>
+          <t>3189386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3163208</t>
+          <t>3189386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3358275</t>
+          <t>3404363</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3358275</t>
+          <t>3404363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3358275</t>
+          <t>3404363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6521482</t>
+          <t>6593749</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6521482</t>
+          <t>6593749</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6521482</t>
+          <t>6593749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
